--- a/site_cluster_comparison.xlsx
+++ b/site_cluster_comparison.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netorg1056155-my.sharepoint.com/personal/a_sharma3_cloudextel_com/Documents/Desktop/SDU-billing-data/sdu-data-import/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_C9A5141F956950826BCB0E5F5F7AD6C2BE00B74B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A561D34-1037-49C4-A852-5A71B59348DF}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_C9A5141F956950826BCB0E5F5F7AD6C2BE00B74B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24F5E832-0F5E-4FC7-B0E1-99B48C81CD23}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6222,6 +6222,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6513,8 +6517,10 @@
   <dimension ref="A1:F628"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
